--- a/reports/OYPB_브랜드별_시딩_비용_광고성과_260907 HAN (최종).xlsx
+++ b/reports/OYPB_브랜드별_시딩_비용_광고성과_260907 HAN (최종).xlsx
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="O8" s="44" t="n">
-        <v>325861024</v>
+        <v>328799970</v>
       </c>
     </row>
     <row r="9" ht="39.6" customHeight="1" s="35">
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="O9" s="44" t="n">
-        <v>115718190</v>
+        <v>116761853</v>
       </c>
     </row>
     <row r="10" ht="39.6" customHeight="1" s="35">
@@ -1173,7 +1173,7 @@
         </is>
       </c>
       <c r="O10" s="44" t="n">
-        <v>107427671</v>
+        <v>108396562</v>
       </c>
     </row>
     <row r="11" ht="39.6" customHeight="1" s="35">
@@ -1227,7 +1227,7 @@
         </is>
       </c>
       <c r="O11" s="44" t="n">
-        <v>66149614</v>
+        <v>66746218</v>
       </c>
     </row>
     <row r="12" ht="39.6" customHeight="1" s="35">
@@ -1278,11 +1278,11 @@
       <c r="N12" s="16" t="inlineStr">
         <is>
           <t>26.06 NAD 크림 나노 시딩 테스트
-조회수·참여 모두 저조</t>
+원고료 건당 333,000 · 조회수·참여 모두 저조</t>
         </is>
       </c>
       <c r="O12" s="44" t="n">
-        <v>2907729</v>
+        <v>4105157</v>
       </c>
     </row>
     <row r="13" ht="39.6" customHeight="1" s="35">
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="O14" s="44" t="n">
-        <v>56707149</v>
+        <v>57218591</v>
       </c>
     </row>
     <row r="15" ht="39.6" customHeight="1" s="35">
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="O15" s="44" t="n">
-        <v>67815249</v>
+        <v>71765393</v>
       </c>
     </row>
     <row r="16" ht="39.6" customHeight="1" s="35">
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="O16" s="44" t="n">
-        <v>39270879</v>
+        <v>39625063</v>
       </c>
     </row>
     <row r="17" ht="39.6" customHeight="1" s="35">
@@ -1554,7 +1554,7 @@
         </is>
       </c>
       <c r="O17" s="44" t="n">
-        <v>67542290</v>
+        <v>55792089</v>
       </c>
     </row>
     <row r="18" ht="39.6" customHeight="1" s="35">
@@ -1609,7 +1609,7 @@
         </is>
       </c>
       <c r="O18" s="44" t="n">
-        <v>6457878</v>
+        <v>6516122</v>
       </c>
     </row>
     <row r="19" ht="39.6" customHeight="1" s="35">
@@ -1663,7 +1663,7 @@
         </is>
       </c>
       <c r="O19" s="44" t="n">
-        <v>10995846</v>
+        <v>11095018</v>
       </c>
     </row>
     <row r="20" ht="26.4" customHeight="1" s="35">
@@ -1717,7 +1717,7 @@
         </is>
       </c>
       <c r="O20" s="44" t="n">
-        <v>3490745</v>
+        <v>3522228</v>
       </c>
     </row>
     <row r="21" ht="26.4" customHeight="1" s="35">
@@ -1783,7 +1783,7 @@
     <row r="22">
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>※ 비용 = 세금계산서 발행 확정 900,344,264원 (26.02~08 확정 840,514,264 + 25년 발행 59,830,000 · 바이오힐보 US 30,000,000 포함). + JP 미발행 8,904,000 → 진행 기준 909,248,264원</t>
+          <t>※ 비용 = 세금계산서 발행 확정 900,344,264원 (26.02~08 확정 840,514,264 + 25년 발행 59,830,000 · 바이오힐보 US 30,000,000 포함). + JP 미발행 8,715,000(21건×415,000) → 진행 기준 909,059,264원</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
     <row r="27">
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>※ (참고) 크리에이터 원고료 498,658,205원 = 청구액의 55.4%. 마크업·VAT·솔루션·지급대행 제외 금액으로 위 단가 산정에는 사용하지 않았다.</t>
+          <t>※ (참고) 크리에이터 원고료 494,201,000원 = 청구액의 54.9%. 국내는 IMD 기재값, JP 99건은 확정 단가(웨이크메이크·컬러그램 건당 415,000 / 바이오힐보 333,000) 기준이다. 위 단가 산정에는 사용하지 않았다.</t>
         </is>
       </c>
     </row>

--- a/reports/OYPB_브랜드별_시딩_비용_광고성과_260907 HAN (최종).xlsx
+++ b/reports/OYPB_브랜드별_시딩_비용_광고성과_260907 HAN (최종).xlsx
@@ -124,7 +124,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -263,6 +263,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
@@ -275,7 +295,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -378,23 +398,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="10" fontId="4" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="9" fontId="4" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="2">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -404,7 +420,7 @@
     <xf numFmtId="164" fontId="4" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="4" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -413,7 +429,7 @@
     <xf numFmtId="164" fontId="5" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="5" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="5" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -423,6 +439,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -824,7 +843,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:O28"/>
+  <dimension ref="B2:Q27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.2"/>
   <cols>
     <col width="8.796875" customWidth="1" style="3" min="1" max="1"/>
@@ -832,16 +851,19 @@
     <col width="10.296875" customWidth="1" style="3" min="3" max="5"/>
     <col width="13.59765625" customWidth="1" style="3" min="6" max="6"/>
     <col width="13.69921875" customWidth="1" style="3" min="7" max="10"/>
-    <col width="13.59765625" customWidth="1" style="3" min="11" max="12"/>
-    <col width="10.296875" customWidth="1" style="3" min="13" max="13"/>
-    <col width="36.8984375" customWidth="1" style="3" min="14" max="14"/>
+    <col width="9" customWidth="1" style="3" min="11" max="12"/>
+    <col width="14" customWidth="1" style="35" min="12" max="12"/>
+    <col width="9" customWidth="1" style="3" min="13" max="13"/>
+    <col width="14" customWidth="1" style="3" min="14" max="14"/>
     <col width="15" customWidth="1" style="3" min="15" max="16384"/>
+    <col width="9" customWidth="1" style="35" min="16" max="16"/>
+    <col width="38" customWidth="1" style="35" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="2" ht="13.8" customHeight="1" s="35">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>OYPB 브랜드별 시딩·비용·광고성과</t>
+          <t>OYPB 브랜드별 시딩 · 원고료 · 성과  (팩트 집계)</t>
         </is>
       </c>
       <c r="C2" s="2" t="n"/>
@@ -860,7 +882,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>※ 통계 : 25.04 ~ 26.09 · 국내외 전체 2,165건(글로벌 167건 = JP 99 + US 68) · 26.09.07 기준</t>
+          <t>※ 통계 : 25.04 ~ 26.09 · 국내외 전체 2,165건(KR 1,998 + 글로벌 167 = JP 99 + US 68) · 26.09.07 기준</t>
         </is>
       </c>
       <c r="C3" s="2" t="n"/>
@@ -879,7 +901,7 @@
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>※ RD : 표준 기준 ⑤ — 수량·비용 전체 2,165건 / 조회수·참여 성과 집계분 2,112건 · 모든 단가는 세금계산서 발행 비용 기준</t>
+          <t>※ RD : 모든 값은 원천 자료 기재값이다. 추정·안분·보정값은 사용하지 않았다.</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -911,47 +933,49 @@
       <c r="N5" s="2" t="n"/>
     </row>
     <row r="6">
-      <c r="B6" s="4" t="n"/>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
           <t>UGC 수량</t>
         </is>
       </c>
       <c r="D6" s="36" t="n"/>
-      <c r="E6" s="37" t="n"/>
-      <c r="F6" s="38" t="inlineStr">
-        <is>
-          <t>콘텐츠 성과</t>
-        </is>
-      </c>
-      <c r="G6" s="36" t="n"/>
+      <c r="E6" s="36" t="n"/>
+      <c r="F6" s="37" t="n"/>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>콘텐츠 성과 (실측)</t>
+        </is>
+      </c>
       <c r="H6" s="36" t="n"/>
       <c r="I6" s="36" t="n"/>
-      <c r="J6" s="37" t="n"/>
-      <c r="K6" s="38" t="inlineStr">
-        <is>
-          <t>퍼포먼스 광고 성과</t>
-        </is>
-      </c>
-      <c r="L6" s="36" t="n"/>
+      <c r="J6" s="36" t="n"/>
+      <c r="K6" s="37" t="n"/>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>원고료</t>
+        </is>
+      </c>
       <c r="M6" s="37" t="n"/>
-      <c r="N6" s="39" t="inlineStr">
+      <c r="N6" s="5" t="inlineStr">
+        <is>
+          <t>퍼포먼스 광고</t>
+        </is>
+      </c>
+      <c r="O6" s="36" t="n"/>
+      <c r="P6" s="37" t="n"/>
+      <c r="Q6" s="5" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="O6" s="40" t="inlineStr">
-        <is>
-          <t>비용</t>
-        </is>
-      </c>
     </row>
     <row r="7">
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
+      <c r="B7" s="38" t="n"/>
       <c r="C7" s="10" t="inlineStr">
         <is>
           <t>KR</t>
@@ -969,50 +993,60 @@
       </c>
       <c r="F7" s="10" t="inlineStr">
         <is>
+          <t>성과 집계</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
           <t>조회수</t>
         </is>
       </c>
-      <c r="G7" s="10" t="inlineStr">
-        <is>
-          <t>평균 조회수</t>
-        </is>
-      </c>
-      <c r="H7" s="11" t="inlineStr">
-        <is>
-          <t>참여수</t>
-        </is>
-      </c>
-      <c r="I7" s="11" t="inlineStr">
-        <is>
-          <t>평균 CPV</t>
-        </is>
-      </c>
-      <c r="J7" s="11" t="inlineStr">
-        <is>
-          <t>평균 CPE</t>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>좋아요</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>댓글</t>
+        </is>
+      </c>
+      <c r="J7" s="10" t="inlineStr">
+        <is>
+          <t>참여</t>
         </is>
       </c>
       <c r="K7" s="10" t="inlineStr">
         <is>
+          <t>ER</t>
+        </is>
+      </c>
+      <c r="L7" s="10" t="inlineStr">
+        <is>
+          <t>원고료</t>
+        </is>
+      </c>
+      <c r="M7" s="10" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="N7" s="10" t="inlineStr">
+        <is>
           <t>광고비</t>
         </is>
       </c>
-      <c r="L7" s="10" t="inlineStr">
+      <c r="O7" s="10" t="inlineStr">
         <is>
           <t>전환 매출</t>
         </is>
       </c>
-      <c r="M7" s="10" t="inlineStr">
+      <c r="P7" s="10" t="inlineStr">
         <is>
           <t>ROAS</t>
         </is>
       </c>
-      <c r="N7" s="41" t="n"/>
-      <c r="O7" s="10" t="inlineStr">
-        <is>
-          <t>세금계산서</t>
-        </is>
-      </c>
+      <c r="Q7" s="38" t="n"/>
     </row>
     <row r="8" ht="39.6" customHeight="1" s="35">
       <c r="B8" s="13" t="inlineStr">
@@ -1020,53 +1054,59 @@
           <t>아이디얼포맨</t>
         </is>
       </c>
-      <c r="C8" s="42" t="n">
+      <c r="C8" s="39" t="n">
         <v>737</v>
       </c>
-      <c r="D8" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="42">
+      <c r="D8" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="39">
         <f>SUM(C8:D8)</f>
         <v/>
       </c>
-      <c r="F8" s="42" t="n">
+      <c r="F8" s="39" t="n">
+        <v>737</v>
+      </c>
+      <c r="G8" s="39" t="n">
         <v>17330588</v>
       </c>
-      <c r="G8" s="42">
-        <f>F8/E8</f>
-        <v/>
-      </c>
-      <c r="H8" s="42" t="n">
-        <v>231083</v>
-      </c>
-      <c r="I8" s="43">
-        <f>O8/F8</f>
-        <v/>
-      </c>
-      <c r="J8" s="42">
-        <f>ROUND(O8/H8,0)</f>
-        <v/>
-      </c>
-      <c r="K8" s="42" t="n">
+      <c r="H8" s="39" t="n">
+        <v>174558</v>
+      </c>
+      <c r="I8" s="39" t="n">
+        <v>11787</v>
+      </c>
+      <c r="J8" s="39">
+        <f>H8+I8</f>
+        <v/>
+      </c>
+      <c r="K8" s="40">
+        <f>J8/G8</f>
+        <v/>
+      </c>
+      <c r="L8" s="39" t="n">
+        <v>186700000</v>
+      </c>
+      <c r="M8" s="15">
+        <f>L8/G8</f>
+        <v/>
+      </c>
+      <c r="N8" s="16" t="n">
         <v>33768439</v>
       </c>
-      <c r="L8" s="42" t="n">
+      <c r="O8" s="41" t="n">
         <v>102736712</v>
       </c>
-      <c r="M8" s="15">
-        <f>L8/K8</f>
-        <v/>
-      </c>
-      <c r="N8" s="16" t="inlineStr">
+      <c r="P8" s="41">
+        <f>O8/N8</f>
+        <v/>
+      </c>
+      <c r="Q8" s="42" t="inlineStr">
         <is>
           <t>25년 4Q UGC 협업 첫 시작을 바탕으로 
 250%대 ROAS는 300% 이상으로 올라 섬</t>
         </is>
       </c>
-      <c r="O8" s="44" t="n">
-        <v>328799970</v>
-      </c>
     </row>
     <row r="9" ht="39.6" customHeight="1" s="35">
       <c r="B9" s="13" t="inlineStr">
@@ -1074,53 +1114,59 @@
           <t>브링그린</t>
         </is>
       </c>
-      <c r="C9" s="42" t="n">
+      <c r="C9" s="39" t="n">
         <v>313</v>
       </c>
-      <c r="D9" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="42">
+      <c r="D9" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="39">
         <f>SUM(C9:D9)</f>
         <v/>
       </c>
-      <c r="F9" s="42" t="n">
+      <c r="F9" s="39" t="n">
+        <v>313</v>
+      </c>
+      <c r="G9" s="39" t="n">
         <v>15535558</v>
       </c>
-      <c r="G9" s="42">
-        <f>F9/E9</f>
-        <v/>
-      </c>
-      <c r="H9" s="42" t="n">
-        <v>59372</v>
-      </c>
-      <c r="I9" s="43">
-        <f>O9/F9</f>
-        <v/>
-      </c>
-      <c r="J9" s="42">
-        <f>ROUND(O9/H9,0)</f>
-        <v/>
-      </c>
-      <c r="K9" s="42" t="n">
+      <c r="H9" s="39" t="n">
+        <v>45278</v>
+      </c>
+      <c r="I9" s="39" t="n">
+        <v>4314</v>
+      </c>
+      <c r="J9" s="39">
+        <f>H9+I9</f>
+        <v/>
+      </c>
+      <c r="K9" s="40">
+        <f>J9/G9</f>
+        <v/>
+      </c>
+      <c r="L9" s="39" t="n">
+        <v>66300000</v>
+      </c>
+      <c r="M9" s="15">
+        <f>L9/G9</f>
+        <v/>
+      </c>
+      <c r="N9" s="16" t="n">
         <v>124304394</v>
       </c>
-      <c r="L9" s="42" t="n">
+      <c r="O9" s="41" t="n">
         <v>729266288</v>
       </c>
-      <c r="M9" s="15">
-        <f>L9/K9</f>
-        <v/>
-      </c>
-      <c r="N9" s="16" t="inlineStr">
+      <c r="P9" s="41">
+        <f>O9/N9</f>
+        <v/>
+      </c>
+      <c r="Q9" s="42" t="inlineStr">
         <is>
           <t>전체 퍼포먼스 광고비 44% 집행 · 전환 매출 49% 창출
 UGC&amp;협력광고 중심 티트리 라인 스케일업 필요</t>
         </is>
       </c>
-      <c r="O9" s="44" t="n">
-        <v>116761853</v>
-      </c>
     </row>
     <row r="10" ht="39.6" customHeight="1" s="35">
       <c r="B10" s="13" t="inlineStr">
@@ -1128,52 +1174,58 @@
           <t>라운드어라운드</t>
         </is>
       </c>
-      <c r="C10" s="42" t="n">
+      <c r="C10" s="39" t="n">
         <v>281</v>
       </c>
-      <c r="D10" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="42">
+      <c r="D10" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="39">
         <f>SUM(C10:D10)</f>
         <v/>
       </c>
-      <c r="F10" s="42" t="n">
+      <c r="F10" s="39" t="n">
+        <v>281</v>
+      </c>
+      <c r="G10" s="39" t="n">
         <v>2413068</v>
       </c>
-      <c r="G10" s="42">
-        <f>F10/E10</f>
-        <v/>
-      </c>
-      <c r="H10" s="42" t="n">
-        <v>47169</v>
-      </c>
-      <c r="I10" s="43">
-        <f>O10/F10</f>
-        <v/>
-      </c>
-      <c r="J10" s="42">
-        <f>ROUND(O10/H10,0)</f>
-        <v/>
-      </c>
-      <c r="K10" s="42" t="n">
+      <c r="H10" s="39" t="n">
+        <v>36628</v>
+      </c>
+      <c r="I10" s="39" t="n">
+        <v>5103</v>
+      </c>
+      <c r="J10" s="39">
+        <f>H10+I10</f>
+        <v/>
+      </c>
+      <c r="K10" s="40">
+        <f>J10/G10</f>
+        <v/>
+      </c>
+      <c r="L10" s="39" t="n">
+        <v>61550000</v>
+      </c>
+      <c r="M10" s="15">
+        <f>L10/G10</f>
+        <v/>
+      </c>
+      <c r="N10" s="16" t="n">
         <v>133848</v>
       </c>
-      <c r="L10" s="42" t="n">
+      <c r="O10" s="41" t="n">
         <v>348140</v>
       </c>
-      <c r="M10" s="15">
-        <f>L10/K10</f>
-        <v/>
-      </c>
-      <c r="N10" s="16" t="inlineStr">
-        <is>
-          <t>PR키트 진행 등 참여율 1위(1.95%)
+      <c r="P10" s="41">
+        <f>O10/N10</f>
+        <v/>
+      </c>
+      <c r="Q10" s="42" t="inlineStr">
+        <is>
+          <t>PR키트 진행 등 참여율 1위(1.73%)
 광고는 281건 중 1건만 집행</t>
         </is>
-      </c>
-      <c r="O10" s="44" t="n">
-        <v>108396562</v>
       </c>
     </row>
     <row r="11" ht="39.6" customHeight="1" s="35">
@@ -1182,53 +1234,59 @@
           <t>바이오힐보 (국내)</t>
         </is>
       </c>
-      <c r="C11" s="42" t="n">
+      <c r="C11" s="39" t="n">
         <v>195</v>
       </c>
-      <c r="D11" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="42">
+      <c r="D11" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="39">
         <f>SUM(C11:D11)</f>
         <v/>
       </c>
-      <c r="F11" s="42" t="n">
+      <c r="F11" s="39" t="n">
+        <v>195</v>
+      </c>
+      <c r="G11" s="39" t="n">
         <v>5440064</v>
       </c>
-      <c r="G11" s="42">
-        <f>F11/E11</f>
-        <v/>
-      </c>
-      <c r="H11" s="42" t="n">
-        <v>29506</v>
-      </c>
-      <c r="I11" s="43">
-        <f>O11/F11</f>
-        <v/>
-      </c>
-      <c r="J11" s="42">
-        <f>ROUND(O11/H11,0)</f>
-        <v/>
-      </c>
-      <c r="K11" s="42" t="n">
+      <c r="H11" s="39" t="n">
+        <v>22032</v>
+      </c>
+      <c r="I11" s="39" t="n">
+        <v>2890</v>
+      </c>
+      <c r="J11" s="39">
+        <f>H11+I11</f>
+        <v/>
+      </c>
+      <c r="K11" s="40">
+        <f>J11/G11</f>
+        <v/>
+      </c>
+      <c r="L11" s="39" t="n">
+        <v>37900000</v>
+      </c>
+      <c r="M11" s="15">
+        <f>L11/G11</f>
+        <v/>
+      </c>
+      <c r="N11" s="16" t="n">
         <v>56333229</v>
       </c>
-      <c r="L11" s="42" t="n">
+      <c r="O11" s="41" t="n">
         <v>172219558</v>
       </c>
-      <c r="M11" s="15">
-        <f>L11/K11</f>
-        <v/>
-      </c>
-      <c r="N11" s="16" t="inlineStr">
+      <c r="P11" s="41">
+        <f>O11/N11</f>
+        <v/>
+      </c>
+      <c r="Q11" s="42" t="inlineStr">
         <is>
           <t>퍼포먼스 광고 성과는 전량 국내에서 발생
 최대 조회수 764,503뷰</t>
         </is>
       </c>
-      <c r="O11" s="44" t="n">
-        <v>66746218</v>
-      </c>
     </row>
     <row r="12" ht="39.6" customHeight="1" s="35">
       <c r="B12" s="13" t="inlineStr">
@@ -1236,53 +1294,59 @@
           <t>바이오힐보 (해외·JP)</t>
         </is>
       </c>
-      <c r="C12" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="42" t="n">
+      <c r="C12" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="39" t="n">
         <v>7</v>
       </c>
-      <c r="E12" s="42">
+      <c r="E12" s="39">
         <f>SUM(C12:D12)</f>
         <v/>
       </c>
-      <c r="F12" s="42" t="n">
+      <c r="F12" s="39" t="n">
+        <v>7</v>
+      </c>
+      <c r="G12" s="39" t="n">
         <v>44255</v>
       </c>
-      <c r="G12" s="42">
-        <f>F12/E12</f>
-        <v/>
-      </c>
-      <c r="H12" s="42" t="n">
-        <v>156</v>
-      </c>
-      <c r="I12" s="43">
-        <f>O12/F12</f>
-        <v/>
-      </c>
-      <c r="J12" s="42">
-        <f>ROUND(O12/H12,0)</f>
-        <v/>
-      </c>
-      <c r="K12" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="15" t="inlineStr">
+      <c r="H12" s="39" t="n">
+        <v>24</v>
+      </c>
+      <c r="I12" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="J12" s="39">
+        <f>H12+I12</f>
+        <v/>
+      </c>
+      <c r="K12" s="40">
+        <f>J12/G12</f>
+        <v/>
+      </c>
+      <c r="L12" s="39" t="n">
+        <v>2331000</v>
+      </c>
+      <c r="M12" s="15">
+        <f>L12/G12</f>
+        <v/>
+      </c>
+      <c r="N12" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="41" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N12" s="16" t="inlineStr">
+      <c r="Q12" s="42" t="inlineStr">
         <is>
           <t>26.06 NAD 크림 나노 시딩 테스트
-원고료 건당 333,000 · 조회수·참여 모두 저조</t>
-        </is>
-      </c>
-      <c r="O12" s="44" t="n">
-        <v>4105157</v>
+원고료 건당 333,000(마크업 포함) · 조회수·참여 저조</t>
+        </is>
       </c>
     </row>
     <row r="13" ht="39.6" customHeight="1" s="35">
@@ -1291,53 +1355,62 @@
           <t>바이오힐보 (해외·US)</t>
         </is>
       </c>
-      <c r="C13" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="42" t="n">
+      <c r="C13" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="39" t="n">
         <v>68</v>
       </c>
-      <c r="E13" s="42">
+      <c r="E13" s="39">
         <f>SUM(C13:D13)</f>
         <v/>
       </c>
-      <c r="F13" s="42" t="n">
+      <c r="F13" s="39" t="n">
+        <v>36</v>
+      </c>
+      <c r="G13" s="39" t="n">
         <v>4739117</v>
       </c>
-      <c r="G13" s="42">
-        <f>F13/E13</f>
-        <v/>
-      </c>
-      <c r="H13" s="42" t="n">
-        <v>24134</v>
-      </c>
-      <c r="I13" s="43">
-        <f>O13/F13</f>
-        <v/>
-      </c>
-      <c r="J13" s="42">
-        <f>ROUND(O13/H13,0)</f>
-        <v/>
-      </c>
-      <c r="K13" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="42" t="n">
-        <v>0</v>
+      <c r="H13" s="39" t="n">
+        <v>23068</v>
+      </c>
+      <c r="I13" s="39" t="n">
+        <v>1066</v>
+      </c>
+      <c r="J13" s="39">
+        <f>H13+I13</f>
+        <v/>
+      </c>
+      <c r="K13" s="40">
+        <f>J13/G13</f>
+        <v/>
+      </c>
+      <c r="L13" s="39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M13" s="15" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N13" s="16" t="inlineStr">
+      <c r="N13" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q13" s="42" t="inlineStr">
         <is>
           <t>68건 중 36건 성과 확보 · 건당 131,642뷰(국내의 4.7배)
-최대 2,954,129뷰 = 전체 1위</t>
-        </is>
-      </c>
-      <c r="O13" s="44" t="n">
-        <v>30000000</v>
+최대 2,954,129뷰 = 전체 1위 · 원고료 데이터 없음</t>
+        </is>
       </c>
     </row>
     <row r="14" ht="39.6" customHeight="1" s="35">
@@ -1346,53 +1419,59 @@
           <t>식물나라</t>
         </is>
       </c>
-      <c r="C14" s="42" t="n">
+      <c r="C14" s="39" t="n">
         <v>140</v>
       </c>
-      <c r="D14" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="42">
+      <c r="D14" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="39">
         <f>SUM(C14:D14)</f>
         <v/>
       </c>
-      <c r="F14" s="42" t="n">
+      <c r="F14" s="39" t="n">
+        <v>140</v>
+      </c>
+      <c r="G14" s="39" t="n">
         <v>2788821</v>
       </c>
-      <c r="G14" s="42">
-        <f>F14/E14</f>
-        <v/>
-      </c>
-      <c r="H14" s="42" t="n">
-        <v>25032</v>
-      </c>
-      <c r="I14" s="43">
-        <f>O14/F14</f>
-        <v/>
-      </c>
-      <c r="J14" s="42">
-        <f>ROUND(O14/H14,0)</f>
-        <v/>
-      </c>
-      <c r="K14" s="42" t="n">
+      <c r="H14" s="39" t="n">
+        <v>17873</v>
+      </c>
+      <c r="I14" s="39" t="n">
+        <v>2446</v>
+      </c>
+      <c r="J14" s="39">
+        <f>H14+I14</f>
+        <v/>
+      </c>
+      <c r="K14" s="40">
+        <f>J14/G14</f>
+        <v/>
+      </c>
+      <c r="L14" s="39" t="n">
+        <v>32490000</v>
+      </c>
+      <c r="M14" s="43">
+        <f>L14/G14</f>
+        <v/>
+      </c>
+      <c r="N14" s="16" t="n">
         <v>14985030</v>
       </c>
-      <c r="L14" s="42" t="n">
+      <c r="O14" s="41" t="n">
         <v>118255596</v>
       </c>
-      <c r="M14" s="45">
-        <f>L14/K14</f>
-        <v/>
-      </c>
-      <c r="N14" s="16" t="inlineStr">
+      <c r="P14" s="41">
+        <f>O14/N14</f>
+        <v/>
+      </c>
+      <c r="Q14" s="42" t="inlineStr">
         <is>
           <t>빅&amp;스몰웨이브의 시작(25.05)
 마이크로 IMC 성과 가장 잘 워킹하는 브랜드</t>
         </is>
       </c>
-      <c r="O14" s="44" t="n">
-        <v>57218591</v>
-      </c>
     </row>
     <row r="15" ht="39.6" customHeight="1" s="35">
       <c r="B15" s="13" t="inlineStr">
@@ -1400,52 +1479,58 @@
           <t>웨이크메이크</t>
         </is>
       </c>
-      <c r="C15" s="42" t="n">
+      <c r="C15" s="39" t="n">
         <v>70</v>
       </c>
-      <c r="D15" s="42" t="n">
+      <c r="D15" s="39" t="n">
         <v>60</v>
       </c>
-      <c r="E15" s="42">
+      <c r="E15" s="39">
         <f>SUM(C15:D15)</f>
         <v/>
       </c>
-      <c r="F15" s="42" t="n">
+      <c r="F15" s="39" t="n">
+        <v>109</v>
+      </c>
+      <c r="G15" s="39" t="n">
         <v>3143931</v>
       </c>
-      <c r="G15" s="42">
-        <f>F15/E15</f>
-        <v/>
-      </c>
-      <c r="H15" s="42" t="n">
-        <v>19540</v>
-      </c>
-      <c r="I15" s="43">
-        <f>O15/F15</f>
-        <v/>
-      </c>
-      <c r="J15" s="42">
-        <f>ROUND(O15/H15,0)</f>
-        <v/>
-      </c>
-      <c r="K15" s="42" t="n">
+      <c r="H15" s="39" t="n">
+        <v>17014</v>
+      </c>
+      <c r="I15" s="39" t="n">
+        <v>1083</v>
+      </c>
+      <c r="J15" s="39">
+        <f>H15+I15</f>
+        <v/>
+      </c>
+      <c r="K15" s="40">
+        <f>J15/G15</f>
+        <v/>
+      </c>
+      <c r="L15" s="39" t="n">
+        <v>40750000</v>
+      </c>
+      <c r="M15" s="15">
+        <f>L15/G15</f>
+        <v/>
+      </c>
+      <c r="N15" s="16" t="n">
         <v>16409851</v>
       </c>
-      <c r="L15" s="42" t="n">
+      <c r="O15" s="41" t="n">
         <v>113788050</v>
       </c>
-      <c r="M15" s="15">
-        <f>L15/K15</f>
-        <v/>
-      </c>
-      <c r="N15" s="16" t="inlineStr">
-        <is>
-          <t>26.04 행사 및 올영픽 등 미존재로
-UGC 협업 수량 증대해도 좋을 것으로 판단</t>
-        </is>
-      </c>
-      <c r="O15" s="44" t="n">
-        <v>71765393</v>
+      <c r="P15" s="41">
+        <f>O15/N15</f>
+        <v/>
+      </c>
+      <c r="Q15" s="42" t="inlineStr">
+        <is>
+          <t>JP 60건 건당 415,000 (21건은 26.09 진행 · 미발행)
+26.04 행사·올영픽 미존재로 협업 수량 증대 여지</t>
+        </is>
       </c>
     </row>
     <row r="16" ht="39.6" customHeight="1" s="35">
@@ -1454,54 +1539,60 @@
           <t>루테카</t>
         </is>
       </c>
-      <c r="C16" s="42" t="n">
+      <c r="C16" s="39" t="n">
         <v>124</v>
       </c>
-      <c r="D16" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="42">
+      <c r="D16" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="39">
         <f>SUM(C16:D16)</f>
         <v/>
       </c>
-      <c r="F16" s="42" t="n">
+      <c r="F16" s="39" t="n">
+        <v>124</v>
+      </c>
+      <c r="G16" s="39" t="n">
         <v>1655285</v>
       </c>
-      <c r="G16" s="42">
-        <f>F16/E16</f>
-        <v/>
-      </c>
-      <c r="H16" s="42" t="n">
-        <v>14046</v>
-      </c>
-      <c r="I16" s="43">
-        <f>O16/F16</f>
-        <v/>
-      </c>
-      <c r="J16" s="42">
-        <f>ROUND(O16/H16,0)</f>
-        <v/>
-      </c>
-      <c r="K16" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="45" t="inlineStr">
+      <c r="H16" s="39" t="n">
+        <v>8025</v>
+      </c>
+      <c r="I16" s="39" t="n">
+        <v>1419</v>
+      </c>
+      <c r="J16" s="39">
+        <f>H16+I16</f>
+        <v/>
+      </c>
+      <c r="K16" s="40">
+        <f>J16/G16</f>
+        <v/>
+      </c>
+      <c r="L16" s="39" t="n">
+        <v>22500000</v>
+      </c>
+      <c r="M16" s="43">
+        <f>L16/G16</f>
+        <v/>
+      </c>
+      <c r="N16" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="41" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N16" s="16" t="inlineStr">
+      <c r="Q16" s="42" t="inlineStr">
         <is>
           <t>퍼포먼스 광고 미집행
 (브랜드 fade out)</t>
         </is>
       </c>
-      <c r="O16" s="44" t="n">
-        <v>39625063</v>
-      </c>
     </row>
     <row r="17" ht="39.6" customHeight="1" s="35">
       <c r="B17" s="13" t="inlineStr">
@@ -1509,52 +1600,58 @@
           <t>컬러그램</t>
         </is>
       </c>
-      <c r="C17" s="42" t="n">
+      <c r="C17" s="39" t="n">
         <v>71</v>
       </c>
-      <c r="D17" s="42" t="n">
+      <c r="D17" s="39" t="n">
         <v>32</v>
       </c>
-      <c r="E17" s="42">
+      <c r="E17" s="39">
         <f>SUM(C17:D17)</f>
         <v/>
       </c>
-      <c r="F17" s="42" t="n">
+      <c r="F17" s="39" t="n">
+        <v>103</v>
+      </c>
+      <c r="G17" s="39" t="n">
         <v>2653321</v>
       </c>
-      <c r="G17" s="42">
-        <f>F17/E17</f>
-        <v/>
-      </c>
-      <c r="H17" s="42" t="n">
-        <v>14526</v>
-      </c>
-      <c r="I17" s="43">
-        <f>O17/F17</f>
-        <v/>
-      </c>
-      <c r="J17" s="42">
-        <f>ROUND(O17/H17,0)</f>
-        <v/>
-      </c>
-      <c r="K17" s="42" t="n">
+      <c r="H17" s="39" t="n">
+        <v>8960</v>
+      </c>
+      <c r="I17" s="39" t="n">
+        <v>1141</v>
+      </c>
+      <c r="J17" s="39">
+        <f>H17+I17</f>
+        <v/>
+      </c>
+      <c r="K17" s="40">
+        <f>J17/G17</f>
+        <v/>
+      </c>
+      <c r="L17" s="39" t="n">
+        <v>31680000</v>
+      </c>
+      <c r="M17" s="15">
+        <f>L17/G17</f>
+        <v/>
+      </c>
+      <c r="N17" s="16" t="n">
         <v>23514230</v>
       </c>
-      <c r="L17" s="42" t="n">
+      <c r="O17" s="41" t="n">
         <v>134432958</v>
       </c>
-      <c r="M17" s="15">
-        <f>L17/K17</f>
-        <v/>
-      </c>
-      <c r="N17" s="16" t="inlineStr">
-        <is>
-          <t>IMD 26.09.07로 103건 확정(v8 77건 → +26)
-조회수 +68% · 광고비 3.1배 · 매출 2.2배 · ROAS 572% 5위</t>
-        </is>
-      </c>
-      <c r="O17" s="44" t="n">
-        <v>55792089</v>
+      <c r="P17" s="41">
+        <f>O17/N17</f>
+        <v/>
+      </c>
+      <c r="Q17" s="42" t="inlineStr">
+        <is>
+          <t>IMD 26.09.07로 103건 확정(v8 77건은 부분집합)
+JP 32건 건당 415,000 · ROAS 572%</t>
+        </is>
       </c>
     </row>
     <row r="18" ht="39.6" customHeight="1" s="35">
@@ -1563,54 +1660,60 @@
           <t>케어플러스</t>
         </is>
       </c>
-      <c r="C18" s="42" t="n">
+      <c r="C18" s="39" t="n">
         <v>32</v>
       </c>
-      <c r="D18" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="42">
+      <c r="D18" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="39">
         <f>SUM(C18:D18)</f>
         <v/>
       </c>
-      <c r="F18" s="42" t="n">
+      <c r="F18" s="39" t="n">
+        <v>32</v>
+      </c>
+      <c r="G18" s="39" t="n">
         <v>188488</v>
       </c>
-      <c r="G18" s="42">
-        <f>F18/E18</f>
-        <v/>
-      </c>
-      <c r="H18" s="42" t="n">
-        <v>1839</v>
-      </c>
-      <c r="I18" s="43">
-        <f>O18/F18</f>
-        <v/>
-      </c>
-      <c r="J18" s="42">
-        <f>ROUND(O18/H18,0)</f>
-        <v/>
-      </c>
-      <c r="K18" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="45" t="inlineStr">
+      <c r="H18" s="39" t="n">
+        <v>1511</v>
+      </c>
+      <c r="I18" s="39" t="n">
+        <v>328</v>
+      </c>
+      <c r="J18" s="39">
+        <f>H18+I18</f>
+        <v/>
+      </c>
+      <c r="K18" s="40">
+        <f>J18/G18</f>
+        <v/>
+      </c>
+      <c r="L18" s="39" t="n">
+        <v>3700000</v>
+      </c>
+      <c r="M18" s="43">
+        <f>L18/G18</f>
+        <v/>
+      </c>
+      <c r="N18" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="41" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N18" s="16" t="inlineStr">
+      <c r="Q18" s="42" t="inlineStr">
         <is>
           <t>26.07 UGC 첫 협업 · 퍼포먼스 광고 미집행
 원고료 마이크로 5건×20만 + 나노 27건×10만</t>
         </is>
       </c>
-      <c r="O18" s="44" t="n">
-        <v>6516122</v>
-      </c>
     </row>
     <row r="19" ht="39.6" customHeight="1" s="35">
       <c r="B19" s="13" t="inlineStr">
@@ -1618,52 +1721,58 @@
           <t>필리밀리</t>
         </is>
       </c>
-      <c r="C19" s="42" t="n">
+      <c r="C19" s="39" t="n">
         <v>27</v>
       </c>
-      <c r="D19" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="42">
+      <c r="D19" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="39">
         <f>SUM(C19:D19)</f>
         <v/>
       </c>
-      <c r="F19" s="42" t="n">
+      <c r="F19" s="39" t="n">
+        <v>27</v>
+      </c>
+      <c r="G19" s="39" t="n">
         <v>1353401</v>
       </c>
-      <c r="G19" s="42">
-        <f>F19/E19</f>
-        <v/>
-      </c>
-      <c r="H19" s="42" t="n">
-        <v>2409</v>
-      </c>
-      <c r="I19" s="43">
-        <f>O19/F19</f>
-        <v/>
-      </c>
-      <c r="J19" s="42">
-        <f>ROUND(O19/H19,0)</f>
-        <v/>
-      </c>
-      <c r="K19" s="42" t="n">
+      <c r="H19" s="39" t="n">
+        <v>1551</v>
+      </c>
+      <c r="I19" s="39" t="n">
+        <v>416</v>
+      </c>
+      <c r="J19" s="39">
+        <f>H19+I19</f>
+        <v/>
+      </c>
+      <c r="K19" s="40">
+        <f>J19/G19</f>
+        <v/>
+      </c>
+      <c r="L19" s="39" t="n">
+        <v>6300000</v>
+      </c>
+      <c r="M19" s="15">
+        <f>L19/G19</f>
+        <v/>
+      </c>
+      <c r="N19" s="44" t="n">
         <v>14086284</v>
       </c>
-      <c r="L19" s="42" t="n">
+      <c r="O19" s="41" t="n">
         <v>121998372</v>
       </c>
-      <c r="M19" s="15">
-        <f>L19/K19</f>
-        <v/>
-      </c>
-      <c r="N19" s="46" t="inlineStr">
+      <c r="P19" s="41">
+        <f>O19/N19</f>
+        <v/>
+      </c>
+      <c r="Q19" s="42" t="inlineStr">
         <is>
           <t>전체 브랜드 중 ROAS 1위(866%)
-최저 CPA 1,121원</t>
-        </is>
-      </c>
-      <c r="O19" s="44" t="n">
-        <v>11095018</v>
+최저 CPA 확보</t>
+        </is>
       </c>
     </row>
     <row r="20" ht="26.4" customHeight="1" s="35">
@@ -1672,169 +1781,178 @@
           <t>올더베러</t>
         </is>
       </c>
-      <c r="C20" s="47" t="n">
+      <c r="C20" s="45" t="n">
         <v>8</v>
       </c>
-      <c r="D20" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="47">
+      <c r="D20" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="45">
         <f>SUM(C20:D20)</f>
         <v/>
       </c>
-      <c r="F20" s="47" t="n">
+      <c r="F20" s="45" t="n">
+        <v>8</v>
+      </c>
+      <c r="G20" s="45" t="n">
         <v>396952</v>
       </c>
-      <c r="G20" s="47">
-        <f>F20/E20</f>
-        <v/>
-      </c>
-      <c r="H20" s="47" t="n">
-        <v>3440</v>
-      </c>
-      <c r="I20" s="48">
-        <f>O20/F20</f>
-        <v/>
-      </c>
-      <c r="J20" s="47">
-        <f>ROUND(O20/H20,0)</f>
-        <v/>
-      </c>
-      <c r="K20" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="49" t="inlineStr">
+      <c r="H20" s="45" t="n">
+        <v>3355</v>
+      </c>
+      <c r="I20" s="45" t="n">
+        <v>85</v>
+      </c>
+      <c r="J20" s="45">
+        <f>H20+I20</f>
+        <v/>
+      </c>
+      <c r="K20" s="46">
+        <f>J20/G20</f>
+        <v/>
+      </c>
+      <c r="L20" s="45" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="M20" s="47">
+        <f>L20/G20</f>
+        <v/>
+      </c>
+      <c r="N20" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="41" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N20" s="16" t="inlineStr">
+      <c r="Q20" s="42" t="inlineStr">
         <is>
           <t>퍼포먼스 광고 미집행</t>
         </is>
-      </c>
-      <c r="O20" s="44" t="n">
-        <v>3522228</v>
       </c>
     </row>
     <row r="21" ht="26.4" customHeight="1" s="35">
       <c r="B21" s="31" t="inlineStr">
         <is>
-          <t>소계</t>
-        </is>
-      </c>
-      <c r="C21" s="50">
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="C21" s="48">
         <f>SUM(C8:C20)</f>
         <v/>
       </c>
-      <c r="D21" s="50">
+      <c r="D21" s="48">
         <f>SUM(D8:D20)</f>
         <v/>
       </c>
-      <c r="E21" s="50">
+      <c r="E21" s="48">
         <f>SUM(E8:E20)</f>
         <v/>
       </c>
-      <c r="F21" s="50">
+      <c r="F21" s="48">
         <f>SUM(F8:F20)</f>
         <v/>
       </c>
-      <c r="G21" s="50">
-        <f>F21/E21</f>
-        <v/>
-      </c>
-      <c r="H21" s="50">
+      <c r="G21" s="48">
+        <f>SUM(G8:G20)</f>
+        <v/>
+      </c>
+      <c r="H21" s="48">
         <f>SUM(H8:H20)</f>
         <v/>
       </c>
-      <c r="I21" s="51">
-        <f>O21/F21</f>
-        <v/>
-      </c>
-      <c r="J21" s="50">
-        <f>ROUND(O21/H21,0)</f>
-        <v/>
-      </c>
-      <c r="K21" s="50">
-        <f>SUM(K8:K20)</f>
-        <v/>
-      </c>
-      <c r="L21" s="50">
+      <c r="I21" s="48">
+        <f>SUM(I8:I20)</f>
+        <v/>
+      </c>
+      <c r="J21" s="48">
+        <f>SUM(J8:J20)</f>
+        <v/>
+      </c>
+      <c r="K21" s="49">
+        <f>J21/G21</f>
+        <v/>
+      </c>
+      <c r="L21" s="48">
         <f>SUM(L8:L20)</f>
         <v/>
       </c>
-      <c r="M21" s="52">
-        <f>L21/K21</f>
-        <v/>
-      </c>
-      <c r="N21" s="53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O21" s="54">
+      <c r="M21" s="50">
+        <f>L21/G21</f>
+        <v/>
+      </c>
+      <c r="N21" s="51">
+        <f>SUM(N8:N20)</f>
+        <v/>
+      </c>
+      <c r="O21" s="52">
         <f>SUM(O8:O20)</f>
         <v/>
+      </c>
+      <c r="P21" s="52">
+        <f>O21/N21</f>
+        <v/>
+      </c>
+      <c r="Q21" s="53" t="inlineStr">
+        <is>
+          <t>수량 2,165 / 성과 집계 2,112</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>※ 비용 = 세금계산서 발행 확정 900,344,264원 (26.02~08 확정 840,514,264 + 25년 발행 59,830,000 · 바이오힐보 US 30,000,000 포함). + JP 미발행 8,715,000(21건×415,000) → 진행 기준 909,059,264원</t>
+          <t>※ 수량 = 글로벌 시딩 라인 자료(JP 99 · US 68) + IMD 집계분 / 성과 집계 = IMD에 성과가 기재된 건수 2,112건 (미집계 53건 = US 32 + JP 26.09 21)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>※ 브랜드별 세금계산서는 발행 총액을 원고료 비율로 안분한 값이다(바이오힐보 US는 실제 청구 30,000,000원 직접 계상). 발행 내역상 브랜드 귀속 미확정 조정액이 있어 안분 처리했다.</t>
+          <t>※ 조회수·좋아요·댓글 = IMD 실측값. 좋아요 데이터가 없는 519건(조회수 8,976,727)은 추정하지 않았으므로 참여·ER은 실제보다 낮게(불리하게) 나온 값이다.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>※ 평균 CPV = 세금계산서 ÷ 조회수 / 평균 CPE = 세금계산서 ÷ 참여수 / 참여수 = 좋아요 + 댓글 → 소계 CPV 15.61원 · CPE 1,907원 · 건당 청구액 415,863원</t>
+          <t>※ 원고료 = 국내는 IMD 행 단위 기재값, JP는 확정 단가(웨이크메이크·컬러그램 건당 415,000 / 바이오힐보 건당 333,000 마크업 포함), 케어플러스는 시딩현황 기재값. 바이오힐보 US는 데이터 없음.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>※ 참여수는 좋아요 데이터 공란 519건(IMD 2,076건의 25.0%)을 브랜드·국가별 좋아요율과 좋아요/댓글비의 중앙값으로 추정해 반영한 값이다 — 좋아요 실측 359,877 + 추정 80,292 = 440,169, 댓글 32,083(전량 실측)</t>
+          <t>※ CPV = 원고료 ÷ 조회수. 브랜드별 세금계산서 귀속은 발행 내역에 브랜드 미귀속액 70,431,189원이 있어 산출하지 않았다.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>※ 미집계 53건(바이오힐보 US 32 + 웨이크메이크JP 26.09 21)은 조회수·참여 데이터가 없어 성과 분모에서 제외했다. 수량·비용에는 포함되어 있다.</t>
+          <t>※ 전체 청구 기준 — 세금계산서 발행 900,344,264원 (26.02~08 확정 840,514,264 + 25년 발행 59,830,000 · 바이오힐보 US 30,000,000 포함) ÷ 조회수 57,682,849 = CPV 15.61원 / ÷ 참여 391,960 = CPE 2,297원 / ÷ 2,165건 = 건당 415,863원</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>※ (참고) 크리에이터 원고료 494,201,000원 = 청구액의 54.9%. 국내는 IMD 기재값, JP 99건은 확정 단가(웨이크메이크·컬러그램 건당 415,000 / 바이오힐보 333,000) 기준이다. 위 단가 산정에는 사용하지 않았다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>※ 컬러그램은 IMD 26.09.07 최신본으로 103건 확정(v8 77건은 부분집합, URL 대조 확인). 다른 브랜드도 동일 누락 가능성이 있어 최신 IMD 확인이 필요하다.</t>
+          <t>※ JP 미발행 8,715,000원(웨이크메이크 21건 × 415,000) 별도 → 진행 기준 909,059,264원</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="N6:N7"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="F6:J6"/>
+  <mergeCells count="6">
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="Q6:Q7"/>
+    <mergeCell ref="G6:K6"/>
+    <mergeCell ref="N6:P6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
